--- a/feedback_forms/018_customer_experience_enhancement_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/018_customer_experience_enhancement_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1_-_5'}</t>
+          <t>1_-_5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1 - 5'}</t>
+          <t>1 - 5</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'6_-_10'}</t>
+          <t>6_-_10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '6 - 10'}</t>
+          <t>6 - 10</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'11_-_15'}</t>
+          <t>11_-_15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '11 - 15'}</t>
+          <t>11 - 15</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'16_-_20'}</t>
+          <t>16_-_20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '16 - 20'}</t>
+          <t>16 - 20</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'product',_'label':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Product', 'label': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'service',_'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Service', 'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'overall',_'label':_'overall'}</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Overall', 'label': 'Overall'}</t>
+          <t>Overall</t>
         </is>
       </c>
     </row>
